--- a/data/trans_dic/P56$nadie-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P56$nadie-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 13,89</t>
+          <t>1,74; 15,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,42</t>
+          <t>0,0; 9,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,85</t>
+          <t>0,0; 10,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 9,52</t>
+          <t>1,47; 8,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,07; 19,26</t>
+          <t>4,59; 19,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,27; 11,76</t>
+          <t>3,91; 11,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,71; 23,11</t>
+          <t>9,36; 22,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 6,26</t>
+          <t>2,57; 6,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,64; 14,8</t>
+          <t>4,43; 14,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 9,7</t>
+          <t>3,55; 9,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,43; 17,07</t>
+          <t>7,33; 16,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 6,35</t>
+          <t>2,61; 6,02</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,55</t>
+          <t>0,0; 78,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,01</t>
+          <t>0,0; 55,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 18,75</t>
+          <t>1,87; 19,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,54</t>
+          <t>0,0; 72,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 41,34</t>
+          <t>4,79; 39,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 9,92</t>
+          <t>0,91; 10,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,24</t>
+          <t>0,0; 53,86</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,25; 38,8</t>
+          <t>7,74; 36,17</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 9,82</t>
+          <t>1,94; 11,15</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,17 +1012,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,53</t>
+          <t>0,0; 50,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,05; 58,52</t>
+          <t>8,06; 61,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,78; 88,01</t>
+          <t>5,31; 89,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,56; 43,71</t>
+          <t>8,39; 41,87</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 16,29</t>
+          <t>1,92; 15,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,12</t>
+          <t>0,0; 9,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 18,46</t>
+          <t>2,62; 17,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,85; 10,15</t>
+          <t>2,94; 9,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,73; 20,21</t>
+          <t>5,12; 19,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 11,48</t>
+          <t>3,66; 10,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,35; 23,44</t>
+          <t>10,85; 24,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 6,94</t>
+          <t>2,89; 6,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,37; 15,49</t>
+          <t>5,49; 14,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 8,96</t>
+          <t>3,0; 8,46</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,94; 19,5</t>
+          <t>9,75; 19,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,46; 6,7</t>
+          <t>3,44; 6,62</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>762; 6131</t>
+          <t>769; 6796</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6441</t>
+          <t>0; 6487</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6151</t>
+          <t>0; 6073</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>943; 6465</t>
+          <t>995; 6026</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4227; 16064</t>
+          <t>3828; 16198</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7941; 21863</t>
+          <t>7276; 21120</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13857; 32989</t>
+          <t>13356; 32619</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5319; 12557</t>
+          <t>5152; 13006</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5924; 18874</t>
+          <t>5647; 18774</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8951; 24666</t>
+          <t>9019; 24276</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14810; 34033</t>
+          <t>14609; 33844</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7050; 17049</t>
+          <t>7003; 16167</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2511</t>
+          <t>0; 3275</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1710</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5926</t>
+          <t>0; 6170</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517; 5083</t>
+          <t>507; 5401</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4843</t>
+          <t>0; 4881</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1845</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1222; 10495</t>
+          <t>1215; 9921</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>395; 4172</t>
+          <t>382; 4210</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5702</t>
+          <t>0; 5878</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 1890</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2651; 14187</t>
+          <t>2829; 13226</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1414; 6793</t>
+          <t>1340; 7711</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 761</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1935,17 +1935,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3402</t>
+          <t>0; 3298</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1493</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1603</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1955,27 +1955,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>521; 3786</t>
+          <t>521; 3949</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 1493</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 1654</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1088; 6951</t>
+          <t>419; 7071</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1108; 5659</t>
+          <t>1086; 5420</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>928; 7867</t>
+          <t>929; 7709</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6377</t>
+          <t>0; 7218</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1821; 13312</t>
+          <t>1886; 12832</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2888; 10305</t>
+          <t>2986; 9894</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5358; 18907</t>
+          <t>4787; 18084</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8002; 23197</t>
+          <t>7394; 22064</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17776; 40263</t>
+          <t>18642; 41348</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7826; 17276</t>
+          <t>7206; 16599</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7614; 21970</t>
+          <t>7792; 21243</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9183; 25148</t>
+          <t>8420; 23752</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24249; 47560</t>
+          <t>23786; 47572</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12145; 23506</t>
+          <t>12066; 23214</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$nadie-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P56$nadie-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 15,4</t>
+          <t>1,74; 16,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,48</t>
+          <t>0,0; 9,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,71</t>
+          <t>0,0; 10,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 8,87</t>
+          <t>1,31; 9,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,59; 19,42</t>
+          <t>4,87; 19,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,91; 11,36</t>
+          <t>3,96; 12,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,36; 22,85</t>
+          <t>9,51; 22,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 6,48</t>
+          <t>2,43; 6,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 14,72</t>
+          <t>4,64; 15,19</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 9,54</t>
+          <t>3,63; 9,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,33; 16,97</t>
+          <t>7,21; 17,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,02</t>
+          <t>2,56; 5,85</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,99</t>
+          <t>0,0; 78,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -867,17 +867,17 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,18</t>
+          <t>0,0; 56,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 19,93</t>
+          <t>1,74; 21,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,11</t>
+          <t>0,0; 72,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -887,17 +887,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 39,08</t>
+          <t>4,54; 39,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 10,01</t>
+          <t>0,79; 9,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,86</t>
+          <t>0,0; 58,3</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,74; 36,17</t>
+          <t>7,76; 35,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 11,15</t>
+          <t>1,62; 10,28</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,92</t>
+          <t>0,0; 44,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,06; 61,04</t>
+          <t>8,1; 58,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,31; 89,53</t>
+          <t>13,25; 90,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,39; 41,87</t>
+          <t>8,81; 41,54</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 15,97</t>
+          <t>1,93; 16,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,19</t>
+          <t>0,0; 8,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 17,8</t>
+          <t>3,2; 16,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,94; 9,75</t>
+          <t>2,78; 9,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,12; 19,33</t>
+          <t>4,9; 18,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 10,92</t>
+          <t>3,54; 10,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,85; 24,07</t>
+          <t>11,01; 23,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,89; 6,66</t>
+          <t>3,17; 6,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,49; 14,98</t>
+          <t>5,42; 15,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,0; 8,46</t>
+          <t>3,3; 8,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,75; 19,51</t>
+          <t>9,5; 19,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,62</t>
+          <t>3,47; 6,75</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8315</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10942</t>
+          <t>11493</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>769; 6796</t>
+          <t>766; 7414</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6487</t>
+          <t>0; 6431</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6073</t>
+          <t>0; 6103</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>995; 6026</t>
+          <t>945; 6501</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3828; 16198</t>
+          <t>4065; 16045</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7276; 21120</t>
+          <t>7357; 22878</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13356; 32619</t>
+          <t>13576; 32664</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5152; 13006</t>
+          <t>5275; 13500</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5647; 18774</t>
+          <t>5914; 19373</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9019; 24276</t>
+          <t>9241; 24110</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14609; 33844</t>
+          <t>14382; 34358</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7003; 16167</t>
+          <t>7419; 16918</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3738</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3275</t>
+          <t>0; 3268</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1722,17 +1722,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6170</t>
+          <t>0; 6272</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>507; 5401</t>
+          <t>496; 6023</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4881</t>
+          <t>0; 4920</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1742,17 +1742,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1215; 9921</t>
+          <t>1154; 10089</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>382; 4210</t>
+          <t>380; 4366</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5878</t>
+          <t>0; 6363</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2829; 13226</t>
+          <t>2839; 13013</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1340; 7711</t>
+          <t>1243; 7880</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>2358</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>3412</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3298</t>
+          <t>0; 3182</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>521; 3949</t>
+          <t>662; 4773</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1970,12 +1970,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>419; 7071</t>
+          <t>1047; 7152</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1086; 5420</t>
+          <t>1350; 6363</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11582</t>
+          <t>12697</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17135</t>
+          <t>18644</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>929; 7709</t>
+          <t>930; 7811</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 7218</t>
+          <t>0; 6366</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1886; 12832</t>
+          <t>2310; 12109</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2986; 9894</t>
+          <t>2998; 10739</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4787; 18084</t>
+          <t>4581; 17262</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7394; 22064</t>
+          <t>7158; 21476</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18642; 41348</t>
+          <t>18906; 41034</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7206; 16599</t>
+          <t>8674; 18647</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7792; 21243</t>
+          <t>7687; 21536</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8420; 23752</t>
+          <t>9259; 24530</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23786; 47572</t>
+          <t>23168; 47464</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12066; 23214</t>
+          <t>13228; 25730</t>
         </is>
       </c>
     </row>
